--- a/PO_ALL_SUPPLIERS_-_see_Supplier_column_20260907.xlsx
+++ b/PO_ALL_SUPPLIERS_-_see_Supplier_column_20260907.xlsx
@@ -493,7 +493,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J65"/>
+  <dimension ref="A1:J72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -628,15 +628,19 @@
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>DYNA DOXYCYCLINE 100MG DYNAPHARM</t>
+          <t>TAB CURAM (AMOXYCILLIN + CLAVULANIC ACID) 625MG SANDOZ</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>Permai Polyclinics KK</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="inlineStr"/>
+          <t>DKSH</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>1800-88-2336  |  creditmgmt.hec@dksh.com</t>
+        </is>
+      </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
           <t>nan</t>
@@ -648,16 +652,16 @@
         </is>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="H10" s="5" t="n">
-        <v>107</v>
+        <v>152</v>
       </c>
       <c r="I10" s="7" t="n">
-        <v>0.17</v>
+        <v>0.98</v>
       </c>
       <c r="J10" s="7" t="n">
-        <v>18.19</v>
+        <v>148.96</v>
       </c>
     </row>
     <row r="11">
@@ -666,19 +670,15 @@
       </c>
       <c r="B11" s="9" t="inlineStr">
         <is>
-          <t>TAB MUCOSOLVAN (AMBROXOL) 30MG DKSH</t>
+          <t>DYNA DOXYCYCLINE 100MG DYNAPHARM</t>
         </is>
       </c>
       <c r="C11" s="9" t="inlineStr">
         <is>
-          <t>DKSH</t>
-        </is>
-      </c>
-      <c r="D11" s="9" t="inlineStr">
-        <is>
-          <t>1800-88-2336  |  creditmgmt.hec@dksh.com</t>
-        </is>
-      </c>
+          <t>Permai Polyclinics KK</t>
+        </is>
+      </c>
+      <c r="D11" s="9" t="inlineStr"/>
       <c r="E11" s="8" t="inlineStr">
         <is>
           <t>nan</t>
@@ -690,16 +690,16 @@
         </is>
       </c>
       <c r="G11" s="8" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="H11" s="8" t="n">
-        <v>140</v>
+        <v>107</v>
       </c>
       <c r="I11" s="10" t="n">
-        <v>0.46</v>
+        <v>0.17</v>
       </c>
       <c r="J11" s="10" t="n">
-        <v>64.40000000000001</v>
+        <v>18.19</v>
       </c>
     </row>
     <row r="12">
@@ -784,15 +784,19 @@
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>TAB NUELIN SR (THEOPHYLLINE) 250MG INOVA</t>
+          <t>CANDACORT CREAM (CLOTRIMAZOLE 1% / HYDROCORTISONE 1% ) 15G HOE</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>Permai Polyclinics KK</t>
-        </is>
-      </c>
-      <c r="D14" s="6" t="inlineStr"/>
+          <t>Pahang Pharmacy</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>016-2160526  |  account2@pahangpharmacy.com.my</t>
+        </is>
+      </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
           <t>nan</t>
@@ -800,20 +804,20 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>TABLET</t>
+          <t>TUBE</t>
         </is>
       </c>
       <c r="G14" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H14" s="5" t="n">
-        <v>56</v>
+        <v>7</v>
       </c>
       <c r="I14" s="7" t="n">
-        <v>0.78</v>
+        <v>8.15</v>
       </c>
       <c r="J14" s="7" t="n">
-        <v>43.68</v>
+        <v>57.05</v>
       </c>
     </row>
     <row r="15">
@@ -822,7 +826,7 @@
       </c>
       <c r="B15" s="9" t="inlineStr">
         <is>
-          <t>SCABOMA LOTION  ( LINDANE 1% ) GLENMARK</t>
+          <t>TAB NUELIN SR (THEOPHYLLINE) 250MG INOVA</t>
         </is>
       </c>
       <c r="C15" s="9" t="inlineStr">
@@ -838,20 +842,20 @@
       </c>
       <c r="F15" s="8" t="inlineStr">
         <is>
-          <t>BOTTLE</t>
+          <t>TABLET</t>
         </is>
       </c>
       <c r="G15" s="8" t="n">
         <v>0</v>
       </c>
       <c r="H15" s="8" t="n">
-        <v>2</v>
+        <v>56</v>
       </c>
       <c r="I15" s="10" t="n">
-        <v>17.5</v>
+        <v>0.78</v>
       </c>
       <c r="J15" s="10" t="n">
-        <v>35</v>
+        <v>43.68</v>
       </c>
     </row>
     <row r="16">
@@ -860,7 +864,7 @@
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>TAB STORVAS C (ATORVASTATIN) 20MG RANBAXY</t>
+          <t>SCABOMA LOTION  ( LINDANE 1% ) GLENMARK</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
@@ -876,20 +880,20 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>TABLET</t>
+          <t>BOTTLE</t>
         </is>
       </c>
       <c r="G16" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H16" s="5" t="n">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="I16" s="7" t="n">
-        <v>0.68</v>
+        <v>17.5</v>
       </c>
       <c r="J16" s="7" t="n">
-        <v>61.2</v>
+        <v>35</v>
       </c>
     </row>
     <row r="17">
@@ -898,7 +902,7 @@
       </c>
       <c r="B17" s="9" t="inlineStr">
         <is>
-          <t>PREVENAR 13 (PNEUMOCOCCAL POLYSACCHARIDE CONJUGATE 13-VALENT) PFIZER</t>
+          <t>TAB STORVAS C (ATORVASTATIN) 20MG RANBAXY</t>
         </is>
       </c>
       <c r="C17" s="9" t="inlineStr">
@@ -914,20 +918,20 @@
       </c>
       <c r="F17" s="8" t="inlineStr">
         <is>
-          <t>DOSE</t>
+          <t>TABLET</t>
         </is>
       </c>
       <c r="G17" s="8" t="n">
         <v>0</v>
       </c>
       <c r="H17" s="8" t="n">
-        <v>2</v>
+        <v>90</v>
       </c>
       <c r="I17" s="10" t="n">
-        <v>219</v>
+        <v>0.68</v>
       </c>
       <c r="J17" s="10" t="n">
-        <v>438</v>
+        <v>61.2</v>
       </c>
     </row>
     <row r="18">
@@ -936,7 +940,7 @@
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>TAB PROGIT ( ITOPRIDE HYDROCHLORIDE ) 50MG PRO MED</t>
+          <t>PREVENAR 13 (PNEUMOCOCCAL POLYSACCHARIDE CONJUGATE 13-VALENT) PFIZER</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
@@ -952,20 +956,20 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>TABLET</t>
+          <t>DOSE</t>
         </is>
       </c>
       <c r="G18" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H18" s="5" t="n">
-        <v>48</v>
+        <v>2</v>
       </c>
       <c r="I18" s="7" t="n">
-        <v>1</v>
+        <v>219</v>
       </c>
       <c r="J18" s="7" t="n">
-        <v>48</v>
+        <v>438</v>
       </c>
     </row>
     <row r="19">
@@ -974,12 +978,12 @@
       </c>
       <c r="B19" s="9" t="inlineStr">
         <is>
-          <t>TAB FORSANEC (ETORICOXIB) 90MG SYNERRV</t>
+          <t>TAB PROGIT ( ITOPRIDE HYDROCHLORIDE ) 50MG PRO MED</t>
         </is>
       </c>
       <c r="C19" s="9" t="inlineStr">
         <is>
-          <t>Dr. Nicholas Neelan Jeremiah</t>
+          <t>Permai Polyclinics KK</t>
         </is>
       </c>
       <c r="D19" s="9" t="inlineStr"/>
@@ -997,13 +1001,13 @@
         <v>0</v>
       </c>
       <c r="H19" s="8" t="n">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="I19" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J19" s="10" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
     </row>
     <row r="20">
@@ -1180,19 +1184,15 @@
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>TAB CURAM (AMOXYCILLIN + CLAVULANIC ACID) 625MG SANDOZ</t>
+          <t>FISHGEL PRISTIN OMEGA-3 FISH OIL (EPA 396MG/DHA 264MG/OMEGA-3 FATTY ACIDS 660MG/VIT E 2IU) 1200MG HOLISTA COLLTECH LIMITED</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>DKSH</t>
-        </is>
-      </c>
-      <c r="D24" s="6" t="inlineStr">
-        <is>
-          <t>1800-88-2336  |  creditmgmt.hec@dksh.com</t>
-        </is>
-      </c>
+          <t>Permai Polyclinics KK</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr"/>
       <c r="E24" s="5" t="inlineStr">
         <is>
           <t>nan</t>
@@ -1200,20 +1200,20 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>TABLET</t>
+          <t>BOTTLE</t>
         </is>
       </c>
       <c r="G24" s="5" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="H24" s="5" t="n">
-        <v>44</v>
+        <v>3</v>
       </c>
       <c r="I24" s="7" t="n">
-        <v>0.98</v>
+        <v>53.93</v>
       </c>
       <c r="J24" s="7" t="n">
-        <v>43.12</v>
+        <v>161.79</v>
       </c>
     </row>
     <row r="25">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t>CANDID EARDROPS (CLOTRIMAZOLE 1%) 15ML GLENMARK</t>
+          <t>CAP BIOZOLE (FLUCANAZOLE) 150MG MEDISPEC</t>
         </is>
       </c>
       <c r="C25" s="9" t="inlineStr">
@@ -1238,20 +1238,20 @@
       </c>
       <c r="F25" s="8" t="inlineStr">
         <is>
-          <t>BOTTLE</t>
+          <t>TABLET</t>
         </is>
       </c>
       <c r="G25" s="8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H25" s="8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I25" s="10" t="n">
-        <v>18.95</v>
+        <v>4.91</v>
       </c>
       <c r="J25" s="10" t="n">
-        <v>75.8</v>
+        <v>24.55</v>
       </c>
     </row>
     <row r="26">
@@ -1260,19 +1260,15 @@
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>SYR COLIMIX (DICYCLOMINE 5MG/ SIMETHICONE 50MG) 90ML XEPA</t>
+          <t>CANDID EARDROPS (CLOTRIMAZOLE 1%) 15ML GLENMARK</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>PharmaExpress</t>
-        </is>
-      </c>
-      <c r="D26" s="6" t="inlineStr">
-        <is>
-          <t>088-393227  |  info@pharmaexpress.com.my</t>
-        </is>
-      </c>
+          <t>Permai Polyclinics KK</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr"/>
       <c r="E26" s="5" t="inlineStr">
         <is>
           <t>nan</t>
@@ -1284,16 +1280,16 @@
         </is>
       </c>
       <c r="G26" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H26" s="5" t="n">
         <v>4</v>
       </c>
       <c r="I26" s="7" t="n">
-        <v>7.55</v>
+        <v>18.95</v>
       </c>
       <c r="J26" s="7" t="n">
-        <v>30.2</v>
+        <v>75.8</v>
       </c>
     </row>
     <row r="27">
@@ -1302,15 +1298,19 @@
       </c>
       <c r="B27" s="9" t="inlineStr">
         <is>
-          <t>FOBANCORT CREAM (FUSIDIC ACID 2% W/W, BETAMETHASONE 0.05% W/W) 15G HOE</t>
+          <t>SYR COLIMIX (DICYCLOMINE 5MG/ SIMETHICONE 50MG) 90ML XEPA</t>
         </is>
       </c>
       <c r="C27" s="9" t="inlineStr">
         <is>
-          <t>Permai Polyclinics KK</t>
-        </is>
-      </c>
-      <c r="D27" s="9" t="inlineStr"/>
+          <t>PharmaExpress</t>
+        </is>
+      </c>
+      <c r="D27" s="9" t="inlineStr">
+        <is>
+          <t>088-393227  |  info@pharmaexpress.com.my</t>
+        </is>
+      </c>
       <c r="E27" s="8" t="inlineStr">
         <is>
           <t>nan</t>
@@ -1318,20 +1318,20 @@
       </c>
       <c r="F27" s="8" t="inlineStr">
         <is>
-          <t>TUBE</t>
+          <t>BOTTLE</t>
         </is>
       </c>
       <c r="G27" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H27" s="8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I27" s="10" t="n">
-        <v>14.3</v>
+        <v>7.55</v>
       </c>
       <c r="J27" s="10" t="n">
-        <v>71.5</v>
+        <v>30.2</v>
       </c>
     </row>
     <row r="28">
@@ -1340,7 +1340,7 @@
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>TAB INOX (ITRACONAZOLE)100MG HOVID</t>
+          <t>TAB HOVASC (AMLODIPINE) 5MG HOVID</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
@@ -1360,16 +1360,16 @@
         </is>
       </c>
       <c r="G28" s="5" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="H28" s="5" t="n">
-        <v>14</v>
+        <v>100</v>
       </c>
       <c r="I28" s="7" t="n">
-        <v>1.73</v>
+        <v>0.24</v>
       </c>
       <c r="J28" s="7" t="n">
-        <v>24.22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="29">
@@ -1378,36 +1378,40 @@
       </c>
       <c r="B29" s="9" t="inlineStr">
         <is>
-          <t>SUPP DIMENHYDRINATE 50MG DRIMINATE Y.S.P</t>
+          <t>DIFFLAM FORTE THROAT SPRAY  (BENZYDAMINE 0.3% W/V) ADULTS &amp; CHILD (&gt;6YRS) INOVA</t>
         </is>
       </c>
       <c r="C29" s="9" t="inlineStr">
         <is>
-          <t>Permai Polyclinics KK</t>
-        </is>
-      </c>
-      <c r="D29" s="9" t="inlineStr"/>
+          <t>Pahang Pharmacy</t>
+        </is>
+      </c>
+      <c r="D29" s="9" t="inlineStr">
+        <is>
+          <t>016-2160526  |  account2@pahangpharmacy.com.my</t>
+        </is>
+      </c>
       <c r="E29" s="8" t="inlineStr">
         <is>
-          <t>DRIMINATE</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="F29" s="8" t="inlineStr">
         <is>
-          <t>SUPPOSITORIES</t>
+          <t>BOTTLE</t>
         </is>
       </c>
       <c r="G29" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H29" s="8" t="n">
         <v>9</v>
       </c>
       <c r="I29" s="10" t="n">
-        <v>1.29</v>
+        <v>32</v>
       </c>
       <c r="J29" s="10" t="n">
-        <v>11.61</v>
+        <v>288</v>
       </c>
     </row>
     <row r="30">
@@ -1416,7 +1420,7 @@
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>INJ MENQUADFI (MENINGOCOCCAL VACCINE) 0.5ML 1D SANOFI</t>
+          <t>FOBANCORT CREAM (FUSIDIC ACID 2% W/W, BETAMETHASONE 0.05% W/W) 15G HOE</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
@@ -1432,20 +1436,20 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>DOSE</t>
+          <t>TUBE</t>
         </is>
       </c>
       <c r="G30" s="5" t="n">
         <v>1</v>
       </c>
       <c r="H30" s="5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I30" s="7" t="n">
-        <v>97</v>
+        <v>14.3</v>
       </c>
       <c r="J30" s="7" t="n">
-        <v>194</v>
+        <v>71.5</v>
       </c>
     </row>
     <row r="31">
@@ -1454,15 +1458,19 @@
       </c>
       <c r="B31" s="9" t="inlineStr">
         <is>
-          <t>TAB FORSANEC (ETORICOXIB) 120MG SYNERRV</t>
+          <t>INJ TROVITE PAIR (THIAMINE HYDROCHLORIDE 250MG/5ML + PYRIDOXINE HYDROCHLORIDE 50MG/5ML + DEXTROSE MONOHYDRATE 1000MG/5ML + ASCORBIC ACID 500MG/5ML + DEXPANTHENOL 5MG/5ML + RIBOFLAVIN SODIUM PHOSPHATE 5.133MG/5ML + NICOTINAMIDE 160MG/5ML) DUOPHARMA</t>
         </is>
       </c>
       <c r="C31" s="9" t="inlineStr">
         <is>
-          <t>Dr. Nicholas Neelan Jeremiah</t>
-        </is>
-      </c>
-      <c r="D31" s="9" t="inlineStr"/>
+          <t>Pahang Pharmacy</t>
+        </is>
+      </c>
+      <c r="D31" s="9" t="inlineStr">
+        <is>
+          <t>016-2160526  |  account2@pahangpharmacy.com.my</t>
+        </is>
+      </c>
       <c r="E31" s="8" t="inlineStr">
         <is>
           <t>nan</t>
@@ -1470,20 +1478,20 @@
       </c>
       <c r="F31" s="8" t="inlineStr">
         <is>
-          <t>TABLET</t>
+          <t>AMPULE PAIR</t>
         </is>
       </c>
       <c r="G31" s="8" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="H31" s="8" t="n">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="I31" s="10" t="n">
-        <v>0</v>
+        <v>35.4</v>
       </c>
       <c r="J31" s="10" t="n">
-        <v>0</v>
+        <v>318.6</v>
       </c>
     </row>
     <row r="32">
@@ -1492,7 +1500,7 @@
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>TAB PARACAP 500MG HEALTH PHARM</t>
+          <t>TAB INOX (ITRACONAZOLE)100MG HOVID</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
@@ -1512,16 +1520,16 @@
         </is>
       </c>
       <c r="G32" s="5" t="n">
-        <v>210</v>
+        <v>8</v>
       </c>
       <c r="H32" s="5" t="n">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="I32" s="7" t="n">
-        <v>0.16</v>
+        <v>1.73</v>
       </c>
       <c r="J32" s="7" t="n">
-        <v>4.8</v>
+        <v>24.22</v>
       </c>
     </row>
     <row r="33">
@@ -1530,40 +1538,36 @@
       </c>
       <c r="B33" s="9" t="inlineStr">
         <is>
-          <t>DUOVENT NEBULE (IPRATROPIUM + FENOTEROL) 4ML UNITHER</t>
+          <t>SUPP DIMENHYDRINATE 50MG DRIMINATE Y.S.P</t>
         </is>
       </c>
       <c r="C33" s="9" t="inlineStr">
         <is>
-          <t>Pahang Pharmacy</t>
-        </is>
-      </c>
-      <c r="D33" s="9" t="inlineStr">
-        <is>
-          <t>016-2160526  |  account2@pahangpharmacy.com.my</t>
-        </is>
-      </c>
+          <t>Permai Polyclinics KK</t>
+        </is>
+      </c>
+      <c r="D33" s="9" t="inlineStr"/>
       <c r="E33" s="8" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>DRIMINATE</t>
         </is>
       </c>
       <c r="F33" s="8" t="inlineStr">
         <is>
-          <t>RESPULE</t>
+          <t>SUPPOSITORIES</t>
         </is>
       </c>
       <c r="G33" s="8" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="H33" s="8" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="I33" s="10" t="n">
-        <v>3.94</v>
+        <v>1.29</v>
       </c>
       <c r="J33" s="10" t="n">
-        <v>43.34</v>
+        <v>11.61</v>
       </c>
     </row>
     <row r="34">
@@ -1572,7 +1576,7 @@
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>TAB DIANE 35 (CYPROTERONE 2MG/ ETHINYLESTRADIOL 0.035MG) BAYER</t>
+          <t>INJ MENQUADFI (MENINGOCOCCAL VACCINE) 0.5ML 1D SANOFI</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
@@ -1588,20 +1592,20 @@
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>TABLET</t>
+          <t>DOSE</t>
         </is>
       </c>
       <c r="G34" s="5" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="H34" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I34" s="7" t="n">
-        <v>2.08</v>
+        <v>97</v>
       </c>
       <c r="J34" s="7" t="n">
-        <v>6.24</v>
+        <v>194</v>
       </c>
     </row>
     <row r="35">
@@ -1610,12 +1614,12 @@
       </c>
       <c r="B35" s="9" t="inlineStr">
         <is>
-          <t>TAB NOVOMIN (DIMENHYDRINATE) 50MG XEPA</t>
+          <t>TAB FORSANEC (ETORICOXIB) 120MG SYNERRV</t>
         </is>
       </c>
       <c r="C35" s="9" t="inlineStr">
         <is>
-          <t>Permai Polyclinics KK</t>
+          <t>Dr. Nicholas Neelan Jeremiah</t>
         </is>
       </c>
       <c r="D35" s="9" t="inlineStr"/>
@@ -1630,16 +1634,16 @@
         </is>
       </c>
       <c r="G35" s="8" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H35" s="8" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I35" s="10" t="n">
-        <v>0.28</v>
+        <v>0</v>
       </c>
       <c r="J35" s="10" t="n">
-        <v>6.44</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -1648,7 +1652,7 @@
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>TAB CONCOR (BISOPROLOL) 5MG MERCKS</t>
+          <t>TAB PARACAP 500MG HEALTH PHARM</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
@@ -1668,16 +1672,16 @@
         </is>
       </c>
       <c r="G36" s="5" t="n">
-        <v>10</v>
+        <v>180</v>
       </c>
       <c r="H36" s="5" t="n">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="I36" s="7" t="n">
-        <v>1.53</v>
+        <v>0.16</v>
       </c>
       <c r="J36" s="7" t="n">
-        <v>30.6</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="37">
@@ -1686,15 +1690,19 @@
       </c>
       <c r="B37" s="9" t="inlineStr">
         <is>
-          <t>SYR SEDILIX-RX LINCTUS (DEXTROMETHORPHAN 15MG/ PROMETHAZINE 3.125MG/ PHENYLEPHRINE 5MG EVERY 5ML)  90ML XEPA</t>
+          <t>TABS BETAMETHASONE 0.5MG Y.S.P.</t>
         </is>
       </c>
       <c r="C37" s="9" t="inlineStr">
         <is>
-          <t>Permai Polyclinics KK</t>
-        </is>
-      </c>
-      <c r="D37" s="9" t="inlineStr"/>
+          <t>UMH Pharmacy</t>
+        </is>
+      </c>
+      <c r="D37" s="9" t="inlineStr">
+        <is>
+          <t>088-215317  |  umhpharmacy@gmail.com</t>
+        </is>
+      </c>
       <c r="E37" s="8" t="inlineStr">
         <is>
           <t>nan</t>
@@ -1702,20 +1710,20 @@
       </c>
       <c r="F37" s="8" t="inlineStr">
         <is>
-          <t>BOTTLE</t>
+          <t>TABLET</t>
         </is>
       </c>
       <c r="G37" s="8" t="n">
+        <v>350</v>
+      </c>
+      <c r="H37" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="H37" s="8" t="n">
-        <v>1</v>
-      </c>
       <c r="I37" s="10" t="n">
-        <v>5.9</v>
+        <v>0.11</v>
       </c>
       <c r="J37" s="10" t="n">
-        <v>5.9</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="38">
@@ -1724,15 +1732,19 @@
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>TAB VELOXIN (MECLOZINE 25MG/PYRIDOXINE 50MG) PHARM-D</t>
+          <t>TAB CLARINASE (PSEUDOEPHEDRINE 120MG, LORATADINE 5MG) BAYER</t>
         </is>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>Permai Polyclinics KK</t>
-        </is>
-      </c>
-      <c r="D38" s="6" t="inlineStr"/>
+          <t>DKSH</t>
+        </is>
+      </c>
+      <c r="D38" s="6" t="inlineStr">
+        <is>
+          <t>1800-88-2336  |  creditmgmt.hec@dksh.com</t>
+        </is>
+      </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
           <t>nan</t>
@@ -1744,16 +1756,16 @@
         </is>
       </c>
       <c r="G38" s="5" t="n">
-        <v>10</v>
+        <v>310</v>
       </c>
       <c r="H38" s="5" t="n">
-        <v>23</v>
+        <v>50</v>
       </c>
       <c r="I38" s="7" t="n">
-        <v>1.06</v>
+        <v>1.81</v>
       </c>
       <c r="J38" s="7" t="n">
-        <v>24.38</v>
+        <v>90.5</v>
       </c>
     </row>
     <row r="39">
@@ -1762,15 +1774,19 @@
       </c>
       <c r="B39" s="9" t="inlineStr">
         <is>
-          <t>TAB DULCOLAX ( BISACODYL ) 5MG SANOFI</t>
+          <t>DUOVENT NEBULE (IPRATROPIUM + FENOTEROL) 4ML UNITHER</t>
         </is>
       </c>
       <c r="C39" s="9" t="inlineStr">
         <is>
-          <t>Permai Polyclinics KK</t>
-        </is>
-      </c>
-      <c r="D39" s="9" t="inlineStr"/>
+          <t>Pahang Pharmacy</t>
+        </is>
+      </c>
+      <c r="D39" s="9" t="inlineStr">
+        <is>
+          <t>016-2160526  |  account2@pahangpharmacy.com.my</t>
+        </is>
+      </c>
       <c r="E39" s="8" t="inlineStr">
         <is>
           <t>nan</t>
@@ -1778,20 +1794,20 @@
       </c>
       <c r="F39" s="8" t="inlineStr">
         <is>
-          <t>TABLET</t>
+          <t>RESPULE</t>
         </is>
       </c>
       <c r="G39" s="8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H39" s="8" t="n">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="I39" s="10" t="n">
-        <v>0.27</v>
+        <v>3.94</v>
       </c>
       <c r="J39" s="10" t="n">
-        <v>12.42</v>
+        <v>43.34</v>
       </c>
     </row>
     <row r="40">
@@ -1800,7 +1816,7 @@
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>TAB EXFORGE 5/80 (AMLODIPINE 5MG/ VALSARTAN 80MG) NORVATIS</t>
+          <t>TAB DIANE 35 (CYPROTERONE 2MG/ ETHINYLESTRADIOL 0.035MG) BAYER</t>
         </is>
       </c>
       <c r="C40" s="6" t="inlineStr">
@@ -1820,16 +1836,16 @@
         </is>
       </c>
       <c r="G40" s="5" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="H40" s="5" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I40" s="7" t="n">
-        <v>2.01</v>
+        <v>2.08</v>
       </c>
       <c r="J40" s="7" t="n">
-        <v>12.06</v>
+        <v>6.24</v>
       </c>
     </row>
     <row r="41">
@@ -1838,19 +1854,15 @@
       </c>
       <c r="B41" s="9" t="inlineStr">
         <is>
-          <t>DIFFLAM FORTE THROAT SPRAY  (BENZYDAMINE 0.3% W/V) ADULTS &amp; CHILD (&gt;6YRS) INOVA</t>
+          <t>TAB NOVOMIN (DIMENHYDRINATE) 50MG XEPA</t>
         </is>
       </c>
       <c r="C41" s="9" t="inlineStr">
         <is>
-          <t>Pahang Pharmacy</t>
-        </is>
-      </c>
-      <c r="D41" s="9" t="inlineStr">
-        <is>
-          <t>016-2160526  |  account2@pahangpharmacy.com.my</t>
-        </is>
-      </c>
+          <t>Permai Polyclinics KK</t>
+        </is>
+      </c>
+      <c r="D41" s="9" t="inlineStr"/>
       <c r="E41" s="8" t="inlineStr">
         <is>
           <t>nan</t>
@@ -1858,20 +1870,20 @@
       </c>
       <c r="F41" s="8" t="inlineStr">
         <is>
-          <t>BOTTLE</t>
+          <t>TABLET</t>
         </is>
       </c>
       <c r="G41" s="8" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="H41" s="8" t="n">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="I41" s="10" t="n">
-        <v>32</v>
+        <v>0.28</v>
       </c>
       <c r="J41" s="10" t="n">
-        <v>256</v>
+        <v>6.44</v>
       </c>
     </row>
     <row r="42">
@@ -1880,19 +1892,15 @@
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>EYE/EAR DROPS DEXTRACIN (DEXAMETHASONE &amp; NEOMYCIN) XEPA</t>
+          <t>TAB CONCOR (BISOPROLOL) 5MG MERCKS</t>
         </is>
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>Pahang Pharmacy</t>
-        </is>
-      </c>
-      <c r="D42" s="6" t="inlineStr">
-        <is>
-          <t>016-2160526  |  account2@pahangpharmacy.com.my</t>
-        </is>
-      </c>
+          <t>Permai Polyclinics KK</t>
+        </is>
+      </c>
+      <c r="D42" s="6" t="inlineStr"/>
       <c r="E42" s="5" t="inlineStr">
         <is>
           <t>nan</t>
@@ -1900,20 +1908,20 @@
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>BOTTLE</t>
+          <t>TABLET</t>
         </is>
       </c>
       <c r="G42" s="5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H42" s="5" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="I42" s="7" t="n">
-        <v>5</v>
+        <v>1.53</v>
       </c>
       <c r="J42" s="7" t="n">
-        <v>30</v>
+        <v>30.6</v>
       </c>
     </row>
     <row r="43">
@@ -1922,7 +1930,7 @@
       </c>
       <c r="B43" s="9" t="inlineStr">
         <is>
-          <t>SYRUP NOVOMIN (DIMENHYDRINATE) 15MG/5ML 60ML (ORANGE FLV) XEPA</t>
+          <t>SYR SEDILIX-RX LINCTUS (DEXTROMETHORPHAN 15MG/ PROMETHAZINE 3.125MG/ PHENYLEPHRINE 5MG EVERY 5ML)  90ML XEPA</t>
         </is>
       </c>
       <c r="C43" s="9" t="inlineStr">
@@ -1942,16 +1950,16 @@
         </is>
       </c>
       <c r="G43" s="8" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="H43" s="8" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I43" s="10" t="n">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="J43" s="10" t="n">
-        <v>27.5</v>
+        <v>11.8</v>
       </c>
     </row>
     <row r="44">
@@ -1960,7 +1968,7 @@
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>TAB COAPROVEL (IRBESARTAN/ HYDROCHOLOTHIAZIDE) 150MG/12.5MG SANOFI</t>
+          <t>TAB VELOXIN (MECLOZINE 25MG/PYRIDOXINE 50MG) PHARM-D</t>
         </is>
       </c>
       <c r="C44" s="6" t="inlineStr">
@@ -1980,16 +1988,16 @@
         </is>
       </c>
       <c r="G44" s="5" t="n">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="H44" s="5" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="I44" s="7" t="n">
-        <v>1.82</v>
+        <v>1.06</v>
       </c>
       <c r="J44" s="7" t="n">
-        <v>54.6</v>
+        <v>24.38</v>
       </c>
     </row>
     <row r="45">
@@ -1998,15 +2006,19 @@
       </c>
       <c r="B45" s="9" t="inlineStr">
         <is>
-          <t>TAB ZENTEL (ALBENDAZOLE) 200MG 2'S HALEON</t>
+          <t>INJ BUFENCON (BETAMETHASONE 7MG/ML) 1ML Y.S.P.</t>
         </is>
       </c>
       <c r="C45" s="9" t="inlineStr">
         <is>
-          <t>Permai Polyclinics KK</t>
-        </is>
-      </c>
-      <c r="D45" s="9" t="inlineStr"/>
+          <t>Pharmex</t>
+        </is>
+      </c>
+      <c r="D45" s="9" t="inlineStr">
+        <is>
+          <t>088-724989</t>
+        </is>
+      </c>
       <c r="E45" s="8" t="inlineStr">
         <is>
           <t>nan</t>
@@ -2014,20 +2026,20 @@
       </c>
       <c r="F45" s="8" t="inlineStr">
         <is>
-          <t>PACKET</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="G45" s="8" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="H45" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I45" s="10" t="n">
-        <v>9.65</v>
+        <v>11.92</v>
       </c>
       <c r="J45" s="10" t="n">
-        <v>9.65</v>
+        <v>35.76</v>
       </c>
     </row>
     <row r="46">
@@ -2036,7 +2048,7 @@
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>CHAMPS D-WORMS SUSPENSION (ALBENDAZOLE 200MG/5ML) 10ML DUOPHARMA</t>
+          <t>TAB DULCOLAX ( BISACODYL ) 5MG SANOFI</t>
         </is>
       </c>
       <c r="C46" s="6" t="inlineStr">
@@ -2052,20 +2064,20 @@
       </c>
       <c r="F46" s="5" t="inlineStr">
         <is>
-          <t>BOTTLE</t>
+          <t>TABLET</t>
         </is>
       </c>
       <c r="G46" s="5" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="H46" s="5" t="n">
-        <v>2</v>
+        <v>46</v>
       </c>
       <c r="I46" s="7" t="n">
-        <v>9.449999999999999</v>
+        <v>0.27</v>
       </c>
       <c r="J46" s="7" t="n">
-        <v>18.9</v>
+        <v>12.42</v>
       </c>
     </row>
     <row r="47">
@@ -2074,15 +2086,19 @@
       </c>
       <c r="B47" s="9" t="inlineStr">
         <is>
-          <t>CREAM CLODERM (CLOBETASOL 0.05% W/W) 15G HOE</t>
+          <t>S/C MOUNJARO (TIRZEPATIDE 25MG/ML) 2.5MG DOSE LILLY</t>
         </is>
       </c>
       <c r="C47" s="9" t="inlineStr">
         <is>
-          <t>Permai Polyclinics KK</t>
-        </is>
-      </c>
-      <c r="D47" s="9" t="inlineStr"/>
+          <t>Zuellig Pharma</t>
+        </is>
+      </c>
+      <c r="D47" s="9" t="inlineStr">
+        <is>
+          <t>088-423500</t>
+        </is>
+      </c>
       <c r="E47" s="8" t="inlineStr">
         <is>
           <t>nan</t>
@@ -2090,20 +2106,20 @@
       </c>
       <c r="F47" s="8" t="inlineStr">
         <is>
-          <t>TUBE</t>
+          <t>DOSE</t>
         </is>
       </c>
       <c r="G47" s="8" t="n">
-        <v>3</v>
+        <v>27.5</v>
       </c>
       <c r="H47" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I47" s="10" t="n">
-        <v>10.5</v>
+        <v>103.67</v>
       </c>
       <c r="J47" s="10" t="n">
-        <v>31.5</v>
+        <v>207.34</v>
       </c>
     </row>
     <row r="48">
@@ -2112,7 +2128,7 @@
       </c>
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>AQUA CREAM (PARAFFIN, WHITE SOFT CREAM) 500GM DUOPHARMA</t>
+          <t>TAB EXFORGE 5/80 (AMLODIPINE 5MG/ VALSARTAN 80MG) NORVATIS</t>
         </is>
       </c>
       <c r="C48" s="6" t="inlineStr">
@@ -2128,20 +2144,20 @@
       </c>
       <c r="F48" s="5" t="inlineStr">
         <is>
-          <t>JAR</t>
+          <t>TABLET</t>
         </is>
       </c>
       <c r="G48" s="5" t="n">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="H48" s="5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I48" s="7" t="n">
-        <v>17</v>
+        <v>2.01</v>
       </c>
       <c r="J48" s="7" t="n">
-        <v>51</v>
+        <v>12.06</v>
       </c>
     </row>
     <row r="49">
@@ -2150,19 +2166,15 @@
       </c>
       <c r="B49" s="9" t="inlineStr">
         <is>
-          <t>BABY DROPS 30ML( VITAMIN A 1333IU, VITAMIN D3 438IU, VITAMIN E 6.57IU, VITAMIN B1 218MCG, VITAMIN B2 336MCG, VITAMIN B6 108MCG, NICOTINAMIDE 2.15MG, TAURINE 15MG, L-LYSINE 20MG PER ML) APPETON</t>
+          <t>NASAL DROPS ILIADIN 0.01% (OXYMETHAZOLINE) DECONGESTANT (&lt; 12MTHS ) P&amp;G</t>
         </is>
       </c>
       <c r="C49" s="9" t="inlineStr">
         <is>
-          <t>Pharmex</t>
-        </is>
-      </c>
-      <c r="D49" s="9" t="inlineStr">
-        <is>
-          <t>088-724989</t>
-        </is>
-      </c>
+          <t>Permai Polyclinics KK</t>
+        </is>
+      </c>
+      <c r="D49" s="9" t="inlineStr"/>
       <c r="E49" s="8" t="inlineStr">
         <is>
           <t>nan</t>
@@ -2174,16 +2186,16 @@
         </is>
       </c>
       <c r="G49" s="8" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="H49" s="8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I49" s="10" t="n">
-        <v>43.29</v>
+        <v>16.56</v>
       </c>
       <c r="J49" s="10" t="n">
-        <v>173.16</v>
+        <v>33.12</v>
       </c>
     </row>
     <row r="50">
@@ -2192,7 +2204,7 @@
       </c>
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>INJ TROVITE PAIR (THIAMINE HYDROCHLORIDE 250MG/5ML + PYRIDOXINE HYDROCHLORIDE 50MG/5ML + DEXTROSE MONOHYDRATE 1000MG/5ML + ASCORBIC ACID 500MG/5ML + DEXPANTHENOL 5MG/5ML + RIBOFLAVIN SODIUM PHOSPHATE 5.133MG/5ML + NICOTINAMIDE 160MG/5ML) DUOPHARMA</t>
+          <t>EYE/EAR DROPS DEXTRACIN (DEXAMETHASONE &amp; NEOMYCIN) XEPA</t>
         </is>
       </c>
       <c r="C50" s="6" t="inlineStr">
@@ -2212,20 +2224,20 @@
       </c>
       <c r="F50" s="5" t="inlineStr">
         <is>
-          <t>AMPULE PAIR</t>
+          <t>BOTTLE</t>
         </is>
       </c>
       <c r="G50" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H50" s="5" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I50" s="7" t="n">
-        <v>35.4</v>
+        <v>5</v>
       </c>
       <c r="J50" s="7" t="n">
-        <v>283.2</v>
+        <v>30</v>
       </c>
     </row>
     <row r="51">
@@ -2234,7 +2246,7 @@
       </c>
       <c r="B51" s="9" t="inlineStr">
         <is>
-          <t>INJECSOL MgSO4 (Magnesium Sulfate 50% W/v 2.465G) 5ML VIAL AIN MEDICARE</t>
+          <t>SYRUP NOVOMIN (DIMENHYDRINATE) 15MG/5ML 60ML (ORANGE FLV) XEPA</t>
         </is>
       </c>
       <c r="C51" s="9" t="inlineStr">
@@ -2250,20 +2262,20 @@
       </c>
       <c r="F51" s="8" t="inlineStr">
         <is>
-          <t>VIAL</t>
+          <t>BOTTLE</t>
         </is>
       </c>
       <c r="G51" s="8" t="n">
         <v>1</v>
       </c>
       <c r="H51" s="8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I51" s="10" t="n">
-        <v>20</v>
+        <v>5.5</v>
       </c>
       <c r="J51" s="10" t="n">
-        <v>80</v>
+        <v>27.5</v>
       </c>
     </row>
     <row r="52">
@@ -2272,7 +2284,7 @@
       </c>
       <c r="B52" s="6" t="inlineStr">
         <is>
-          <t>INJ AMINOPHYLLIN 250MG/10ML FRESENIUS</t>
+          <t>TAB COAPROVEL (IRBESARTAN/ HYDROCHOLOTHIAZIDE) 150MG/12.5MG SANOFI</t>
         </is>
       </c>
       <c r="C52" s="6" t="inlineStr">
@@ -2288,20 +2300,20 @@
       </c>
       <c r="F52" s="5" t="inlineStr">
         <is>
-          <t>VIAL</t>
+          <t>TABLET</t>
         </is>
       </c>
       <c r="G52" s="5" t="n">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="H52" s="5" t="n">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="I52" s="7" t="n">
-        <v>8.5</v>
+        <v>1.82</v>
       </c>
       <c r="J52" s="7" t="n">
-        <v>76.5</v>
+        <v>54.6</v>
       </c>
     </row>
     <row r="53">
@@ -2310,7 +2322,7 @@
       </c>
       <c r="B53" s="9" t="inlineStr">
         <is>
-          <t>INJ ACIPAN (ATROPINE SULPHATE) 1MG/ML 1ML DUOPHARMA</t>
+          <t>TAB ZENTEL (ALBENDAZOLE) 200MG 2'S HALEON</t>
         </is>
       </c>
       <c r="C53" s="9" t="inlineStr">
@@ -2326,20 +2338,20 @@
       </c>
       <c r="F53" s="8" t="inlineStr">
         <is>
-          <t>VIAL</t>
+          <t>PACKET</t>
         </is>
       </c>
       <c r="G53" s="8" t="n">
         <v>2</v>
       </c>
       <c r="H53" s="8" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="I53" s="10" t="n">
-        <v>2.32</v>
+        <v>9.65</v>
       </c>
       <c r="J53" s="10" t="n">
-        <v>20.88</v>
+        <v>9.65</v>
       </c>
     </row>
     <row r="54">
@@ -2348,19 +2360,15 @@
       </c>
       <c r="B54" s="6" t="inlineStr">
         <is>
-          <t>CANDACORT CREAM (CLOTRIMAZOLE 1% / HYDROCORTISONE 1% ) 15G HOE</t>
+          <t>CHAMPS D-WORMS SUSPENSION (ALBENDAZOLE 200MG/5ML) 10ML DUOPHARMA</t>
         </is>
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>Pahang Pharmacy</t>
-        </is>
-      </c>
-      <c r="D54" s="6" t="inlineStr">
-        <is>
-          <t>016-2160526  |  account2@pahangpharmacy.com.my</t>
-        </is>
-      </c>
+          <t>Permai Polyclinics KK</t>
+        </is>
+      </c>
+      <c r="D54" s="6" t="inlineStr"/>
       <c r="E54" s="5" t="inlineStr">
         <is>
           <t>nan</t>
@@ -2368,20 +2376,20 @@
       </c>
       <c r="F54" s="5" t="inlineStr">
         <is>
-          <t>TUBE</t>
+          <t>BOTTLE</t>
         </is>
       </c>
       <c r="G54" s="5" t="n">
         <v>1</v>
       </c>
       <c r="H54" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I54" s="7" t="n">
-        <v>8.15</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="J54" s="7" t="n">
-        <v>32.6</v>
+        <v>18.9</v>
       </c>
     </row>
     <row r="55">
@@ -2390,19 +2398,15 @@
       </c>
       <c r="B55" s="9" t="inlineStr">
         <is>
-          <t>INJ TT VACCINE (TETANUS) 0.5ML SM PHARMA</t>
+          <t>CREAM CLODERM (CLOBETASOL 0.05% W/W) 15G HOE</t>
         </is>
       </c>
       <c r="C55" s="9" t="inlineStr">
         <is>
-          <t>Pharmex</t>
-        </is>
-      </c>
-      <c r="D55" s="9" t="inlineStr">
-        <is>
-          <t>088-724989</t>
-        </is>
-      </c>
+          <t>Permai Polyclinics KK</t>
+        </is>
+      </c>
+      <c r="D55" s="9" t="inlineStr"/>
       <c r="E55" s="8" t="inlineStr">
         <is>
           <t>nan</t>
@@ -2410,20 +2414,20 @@
       </c>
       <c r="F55" s="8" t="inlineStr">
         <is>
-          <t>0.5ML</t>
+          <t>TUBE</t>
         </is>
       </c>
       <c r="G55" s="8" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H55" s="8" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I55" s="10" t="n">
-        <v>3.75</v>
+        <v>10.5</v>
       </c>
       <c r="J55" s="10" t="n">
-        <v>22.5</v>
+        <v>31.5</v>
       </c>
     </row>
     <row r="56">
@@ -2432,7 +2436,7 @@
       </c>
       <c r="B56" s="6" t="inlineStr">
         <is>
-          <t>PNEUMOVAX 23 ( PNEUMOCOCCAL VACCINE POLYVALENT) MSD</t>
+          <t>AQUA CREAM (PARAFFIN, WHITE SOFT CREAM) 500GM DUOPHARMA</t>
         </is>
       </c>
       <c r="C56" s="6" t="inlineStr">
@@ -2448,20 +2452,20 @@
       </c>
       <c r="F56" s="5" t="inlineStr">
         <is>
-          <t>DOSE</t>
+          <t>JAR</t>
         </is>
       </c>
       <c r="G56" s="5" t="n">
         <v>1</v>
       </c>
       <c r="H56" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I56" s="7" t="n">
-        <v>106.5</v>
+        <v>17</v>
       </c>
       <c r="J56" s="7" t="n">
-        <v>106.5</v>
+        <v>51</v>
       </c>
     </row>
     <row r="57">
@@ -2470,15 +2474,19 @@
       </c>
       <c r="B57" s="9" t="inlineStr">
         <is>
-          <t>TAB TELWSIFT (TELMISARTAN) 40MG SYNERRV</t>
+          <t>BABY DROPS 30ML( VITAMIN A 1333IU, VITAMIN D3 438IU, VITAMIN E 6.57IU, VITAMIN B1 218MCG, VITAMIN B2 336MCG, VITAMIN B6 108MCG, NICOTINAMIDE 2.15MG, TAURINE 15MG, L-LYSINE 20MG PER ML) APPETON</t>
         </is>
       </c>
       <c r="C57" s="9" t="inlineStr">
         <is>
-          <t>Dr. Nicholas Neelan Jeremiah</t>
-        </is>
-      </c>
-      <c r="D57" s="9" t="inlineStr"/>
+          <t>Pharmex</t>
+        </is>
+      </c>
+      <c r="D57" s="9" t="inlineStr">
+        <is>
+          <t>088-724989</t>
+        </is>
+      </c>
       <c r="E57" s="8" t="inlineStr">
         <is>
           <t>nan</t>
@@ -2486,20 +2494,20 @@
       </c>
       <c r="F57" s="8" t="inlineStr">
         <is>
-          <t>TABLET</t>
+          <t>BOTTLE</t>
         </is>
       </c>
       <c r="G57" s="8" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H57" s="8" t="n">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="I57" s="10" t="n">
-        <v>0</v>
+        <v>43.29</v>
       </c>
       <c r="J57" s="10" t="n">
-        <v>0</v>
+        <v>173.16</v>
       </c>
     </row>
     <row r="58">
@@ -2508,12 +2516,12 @@
       </c>
       <c r="B58" s="6" t="inlineStr">
         <is>
-          <t>INJ AMSUBAC (AMPICILLIN 1000MG/ SULBACTAM 500MG) 1.5 G AVERROES PHARMACEUTICALS SDN. BHD.</t>
+          <t>INJECSOL MgSO4 (Magnesium Sulfate 50% W/v 2.465G) 5ML VIAL AIN MEDICARE</t>
         </is>
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
-          <t>Dr. Nicholas Neelan Jeremiah</t>
+          <t>Permai Polyclinics KK</t>
         </is>
       </c>
       <c r="D58" s="6" t="inlineStr"/>
@@ -2524,20 +2532,20 @@
       </c>
       <c r="F58" s="5" t="inlineStr">
         <is>
-          <t>AMPULE</t>
+          <t>VIAL</t>
         </is>
       </c>
       <c r="G58" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H58" s="5" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="I58" s="7" t="n">
-        <v>7.4</v>
+        <v>20</v>
       </c>
       <c r="J58" s="7" t="n">
-        <v>66.59999999999999</v>
+        <v>80</v>
       </c>
     </row>
     <row r="59">
@@ -2546,12 +2554,12 @@
       </c>
       <c r="B59" s="9" t="inlineStr">
         <is>
-          <t>REPARIL ICE-SPRAY 200ML VOLCKE AEROSOL ITALY SRL</t>
+          <t>INJ AMINOPHYLLIN 250MG/10ML FRESENIUS</t>
         </is>
       </c>
       <c r="C59" s="9" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>Permai Polyclinics KK</t>
         </is>
       </c>
       <c r="D59" s="9" t="inlineStr"/>
@@ -2562,20 +2570,20 @@
       </c>
       <c r="F59" s="8" t="inlineStr">
         <is>
-          <t>BOTTLE</t>
+          <t>VIAL</t>
         </is>
       </c>
       <c r="G59" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H59" s="8" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="I59" s="10" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="J59" s="10" t="n">
-        <v>0</v>
+        <v>76.5</v>
       </c>
     </row>
     <row r="60">
@@ -2584,12 +2592,12 @@
       </c>
       <c r="B60" s="6" t="inlineStr">
         <is>
-          <t>SYR FLUHALT ( OSELTAMIVIR 60MG/5ML ) 100ML RANBAXY</t>
+          <t>INJ ACIPAN (ATROPINE SULPHATE) 1MG/ML 1ML DUOPHARMA</t>
         </is>
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>Permai Polyclinics KK</t>
         </is>
       </c>
       <c r="D60" s="6" t="inlineStr"/>
@@ -2600,48 +2608,322 @@
       </c>
       <c r="F60" s="5" t="inlineStr">
         <is>
+          <t>VIAL</t>
+        </is>
+      </c>
+      <c r="G60" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="H60" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="I60" s="7" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="J60" s="7" t="n">
+        <v>20.88</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="8" t="n">
+        <v>52</v>
+      </c>
+      <c r="B61" s="9" t="inlineStr">
+        <is>
+          <t>CERUMOL EAR WAX SOFTNER DROPS 10ML</t>
+        </is>
+      </c>
+      <c r="C61" s="9" t="inlineStr">
+        <is>
+          <t>Pahang Pharmacy</t>
+        </is>
+      </c>
+      <c r="D61" s="9" t="inlineStr">
+        <is>
+          <t>016-2160526  |  account2@pahangpharmacy.com.my</t>
+        </is>
+      </c>
+      <c r="E61" s="8" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F61" s="8" t="inlineStr">
+        <is>
           <t>BOTTLE</t>
         </is>
       </c>
-      <c r="G60" s="5" t="n">
+      <c r="G61" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="H61" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="I61" s="10" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="J61" s="10" t="n">
+        <v>37.5</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="5" t="n">
+        <v>53</v>
+      </c>
+      <c r="B62" s="6" t="inlineStr">
+        <is>
+          <t>INJ TT VACCINE (TETANUS) 0.5ML SM PHARMA</t>
+        </is>
+      </c>
+      <c r="C62" s="6" t="inlineStr">
+        <is>
+          <t>Pharmex</t>
+        </is>
+      </c>
+      <c r="D62" s="6" t="inlineStr">
+        <is>
+          <t>088-724989</t>
+        </is>
+      </c>
+      <c r="E62" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F62" s="5" t="inlineStr">
+        <is>
+          <t>0.5ML</t>
+        </is>
+      </c>
+      <c r="G62" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="H62" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="I62" s="7" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="J62" s="7" t="n">
+        <v>26.25</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="8" t="n">
+        <v>54</v>
+      </c>
+      <c r="B63" s="9" t="inlineStr">
+        <is>
+          <t>PNEUMOVAX 23 ( PNEUMOCOCCAL VACCINE POLYVALENT) MSD</t>
+        </is>
+      </c>
+      <c r="C63" s="9" t="inlineStr">
+        <is>
+          <t>Permai Polyclinics KK</t>
+        </is>
+      </c>
+      <c r="D63" s="9" t="inlineStr"/>
+      <c r="E63" s="8" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F63" s="8" t="inlineStr">
+        <is>
+          <t>DOSE</t>
+        </is>
+      </c>
+      <c r="G63" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H63" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I63" s="10" t="n">
+        <v>106.5</v>
+      </c>
+      <c r="J63" s="10" t="n">
+        <v>106.5</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="5" t="n">
+        <v>55</v>
+      </c>
+      <c r="B64" s="6" t="inlineStr">
+        <is>
+          <t>TAB TELWSIFT (TELMISARTAN) 40MG SYNERRV</t>
+        </is>
+      </c>
+      <c r="C64" s="6" t="inlineStr">
+        <is>
+          <t>Dr. Nicholas Neelan Jeremiah</t>
+        </is>
+      </c>
+      <c r="D64" s="6" t="inlineStr"/>
+      <c r="E64" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F64" s="5" t="inlineStr">
+        <is>
+          <t>TABLET</t>
+        </is>
+      </c>
+      <c r="G64" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H64" s="5" t="n">
+        <v>31</v>
+      </c>
+      <c r="I64" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J64" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="8" t="n">
+        <v>56</v>
+      </c>
+      <c r="B65" s="9" t="inlineStr">
+        <is>
+          <t>INJ AMSUBAC (AMPICILLIN 1000MG/ SULBACTAM 500MG) 1.5 G AVERROES PHARMACEUTICALS SDN. BHD.</t>
+        </is>
+      </c>
+      <c r="C65" s="9" t="inlineStr">
+        <is>
+          <t>Dr. Nicholas Neelan Jeremiah</t>
+        </is>
+      </c>
+      <c r="D65" s="9" t="inlineStr"/>
+      <c r="E65" s="8" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F65" s="8" t="inlineStr">
+        <is>
+          <t>AMPULE</t>
+        </is>
+      </c>
+      <c r="G65" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H65" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="I65" s="10" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="J65" s="10" t="n">
+        <v>66.59999999999999</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="5" t="n">
+        <v>57</v>
+      </c>
+      <c r="B66" s="6" t="inlineStr">
+        <is>
+          <t>REPARIL ICE-SPRAY 200ML VOLCKE AEROSOL ITALY SRL</t>
+        </is>
+      </c>
+      <c r="C66" s="6" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="D66" s="6" t="inlineStr"/>
+      <c r="E66" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F66" s="5" t="inlineStr">
+        <is>
+          <t>BOTTLE</t>
+        </is>
+      </c>
+      <c r="G66" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H66" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I66" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J66" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="8" t="n">
+        <v>58</v>
+      </c>
+      <c r="B67" s="9" t="inlineStr">
+        <is>
+          <t>SYR FLUHALT ( OSELTAMIVIR 60MG/5ML ) 100ML RANBAXY</t>
+        </is>
+      </c>
+      <c r="C67" s="9" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="D67" s="9" t="inlineStr"/>
+      <c r="E67" s="8" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F67" s="8" t="inlineStr">
+        <is>
+          <t>BOTTLE</t>
+        </is>
+      </c>
+      <c r="G67" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="H60" s="5" t="n">
+      <c r="H67" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="I60" s="7" t="n">
+      <c r="I67" s="10" t="n">
         <v>121.2</v>
       </c>
-      <c r="J60" s="7" t="n">
+      <c r="J67" s="10" t="n">
         <v>727.2</v>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="11" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="11" t="inlineStr">
         <is>
           <t>GRAND TOTAL</t>
         </is>
       </c>
-      <c r="J61" s="12" t="n">
-        <v>3996.15</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>Total line items: 51</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>Generated: 2026-09-07 07:07</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="13" t="inlineStr">
+      <c r="J68" s="12" t="n">
+        <v>4759.549999999999</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Total line items: 58</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Generated: 2026-09-07 08:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="13" t="inlineStr">
         <is>
           <t>Note: Unit costs are from latest purchase price. Verify with supplier before confirming order.</t>
         </is>
@@ -2650,7 +2932,7 @@
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A61:I61"/>
+    <mergeCell ref="A68:I68"/>
     <mergeCell ref="A2:J2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
